--- a/systolicBloodPressure.xlsx
+++ b/systolicBloodPressure.xlsx
@@ -1,35 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk-my.sharepoint.com/personal/amolina6_utk_edu/Documents/Documents/Courses/AGNR220/fall2025/datafiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk-my.sharepoint.com/personal/amolina6_utk_edu/Documents/Documents/projects/AGNR_220/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{AB9C0292-2AAF-4023-8713-4EB3FD6E14FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B260F942-03E6-4EC1-82EE-804EA294CCEA}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{AB9C0292-2AAF-4023-8713-4EB3FD6E14FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813B02EF-1E55-4A0B-BA26-2B36D16AD8D6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68120915-3A09-454B-B1E0-C35F767053CF}"/>
+    <workbookView minimized="1" xWindow="960" yWindow="900" windowWidth="17280" windowHeight="10005" xr2:uid="{68120915-3A09-454B-B1E0-C35F767053CF}"/>
   </bookViews>
   <sheets>
     <sheet name="systolicBloodPressure" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">systolicBloodPressure!$B$2:$B$102</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">systolicBloodPressure!$B$2:$B$102</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>systolicBP</t>
   </si>
   <si>
     <t>Observation</t>
+  </si>
+  <si>
+    <t>MEAN</t>
+  </si>
+  <si>
+    <t>MEDIAN</t>
+  </si>
+  <si>
+    <t>y-mean</t>
+  </si>
+  <si>
+    <t>y-mean sq</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>variance</t>
+  </si>
+  <si>
+    <t>SD</t>
   </si>
 </sst>
 </file>
@@ -172,7 +205,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,6 +383,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -513,8 +552,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -578,7 +618,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1204,8 +1244,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6629400" y="2185987"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="6648450" y="2102167"/>
+              <a:ext cx="4572000" cy="2636520"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1555,826 +1595,1277 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B0BC50-1829-4E52-B6F0-F8EB26FF6891}">
-  <dimension ref="A1:B102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D105"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>88</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2">
+        <f>B2-$B$104</f>
+        <v>-34.732673267326732</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <f t="shared" ref="C3:C66" si="0">B3-$B$104</f>
+        <v>-34.732673267326732</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>92</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>-30.732673267326732</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>-26.732673267326732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>96</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>-26.732673267326732</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <f>B7-$B$104</f>
+        <v>-22.732673267326732</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>102</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>-20.732673267326732</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>102</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>-20.732673267326732</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>104</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>-18.732673267326732</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>104</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>-18.732673267326732</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>105</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>-17.732673267326732</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>105</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>-17.732673267326732</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>105</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>-17.732673267326732</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>107</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>-15.732673267326732</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>107</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>-15.732673267326732</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>108</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>-14.732673267326732</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>110</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>-12.732673267326732</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>110</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>-12.732673267326732</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>110</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>-12.732673267326732</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>111</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>-11.732673267326732</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>111</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>-11.732673267326732</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>112</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>-10.732673267326732</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
         <v>113</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>-9.7326732673267315</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
         <v>114</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>-8.7326732673267315</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
         <v>114</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>-8.7326732673267315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>115</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>-7.7326732673267315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
         <v>115</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>-7.7326732673267315</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
         <v>116</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>-6.7326732673267315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
         <v>116</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>-6.7326732673267315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
         <v>117</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>-5.7326732673267315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
         <v>117</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>-5.7326732673267315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
         <v>117</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>-5.7326732673267315</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
         <v>117</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>-5.7326732673267315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
         <v>117</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>-5.7326732673267315</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
         <v>117</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>-5.7326732673267315</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
         <v>119</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>-3.7326732673267315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
         <v>119</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>-3.7326732673267315</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>-2.7326732673267315</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
         <v>121</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>-1.7326732673267315</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
         <v>121</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>-1.7326732673267315</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
         <v>121</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>-1.7326732673267315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
         <v>121</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>-1.7326732673267315</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
         <v>121</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>-1.7326732673267315</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
         <v>121</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>-1.7326732673267315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
         <v>122</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>-0.73267326732673155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
         <v>122</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>-0.73267326732673155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
         <v>123</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>0.26732673267326845</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
         <v>123</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>0.26732673267326845</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
         <v>123</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50">
+        <f t="shared" si="0"/>
+        <v>0.26732673267326845</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
         <v>123</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="C51">
+        <f t="shared" si="0"/>
+        <v>0.26732673267326845</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="1">
         <v>123</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <f t="shared" si="0"/>
+        <v>0.26732673267326845</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
         <v>124</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <f t="shared" si="0"/>
+        <v>1.2673267326732685</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
         <v>124</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <f t="shared" si="0"/>
+        <v>1.2673267326732685</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
         <v>124</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <f t="shared" si="0"/>
+        <v>1.2673267326732685</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
         <v>124</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56">
+        <f t="shared" si="0"/>
+        <v>1.2673267326732685</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
         <v>125</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <f t="shared" si="0"/>
+        <v>2.2673267326732685</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58">
         <v>125</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C58">
+        <f t="shared" si="0"/>
+        <v>2.2673267326732685</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
         <v>125</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <f t="shared" si="0"/>
+        <v>2.2673267326732685</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
         <v>126</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <f t="shared" si="0"/>
+        <v>3.2673267326732685</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
         <v>126</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <f t="shared" si="0"/>
+        <v>3.2673267326732685</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
         <v>126</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C62">
+        <f t="shared" si="0"/>
+        <v>3.2673267326732685</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
         <v>126</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C63">
+        <f t="shared" si="0"/>
+        <v>3.2673267326732685</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
         <v>126</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C64">
+        <f t="shared" si="0"/>
+        <v>3.2673267326732685</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65">
         <v>127</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C65">
+        <f t="shared" si="0"/>
+        <v>4.2673267326732685</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
         <v>127</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C66">
+        <f t="shared" si="0"/>
+        <v>4.2673267326732685</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67">
         <v>128</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <f t="shared" ref="C67:C102" si="1">B67-$B$104</f>
+        <v>5.2673267326732685</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68">
         <v>128</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C68">
+        <f t="shared" si="1"/>
+        <v>5.2673267326732685</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
         <v>128</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C69">
+        <f t="shared" si="1"/>
+        <v>5.2673267326732685</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
         <v>128</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C70">
+        <f t="shared" si="1"/>
+        <v>5.2673267326732685</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71">
         <v>129</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C71">
+        <f t="shared" si="1"/>
+        <v>6.2673267326732685</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72">
         <v>129</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C72">
+        <f t="shared" si="1"/>
+        <v>6.2673267326732685</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
         <v>130</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C73">
+        <f t="shared" si="1"/>
+        <v>7.2673267326732685</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74">
         <v>131</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C74">
+        <f t="shared" si="1"/>
+        <v>8.2673267326732685</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75">
         <v>131</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C75">
+        <f t="shared" si="1"/>
+        <v>8.2673267326732685</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76">
         <v>131</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C76">
+        <f t="shared" si="1"/>
+        <v>8.2673267326732685</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="1">
         <v>131</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C77">
+        <f t="shared" si="1"/>
+        <v>8.2673267326732685</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78">
         <v>131</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C78">
+        <f t="shared" si="1"/>
+        <v>8.2673267326732685</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79">
         <v>131</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C79">
+        <f t="shared" si="1"/>
+        <v>8.2673267326732685</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80">
         <v>133</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C80">
+        <f t="shared" si="1"/>
+        <v>10.267326732673268</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
         <v>133</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C81">
+        <f t="shared" si="1"/>
+        <v>10.267326732673268</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82">
         <v>133</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <f t="shared" si="1"/>
+        <v>10.267326732673268</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83">
         <v>134</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <f t="shared" si="1"/>
+        <v>11.267326732673268</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84">
         <v>135</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <f t="shared" si="1"/>
+        <v>12.267326732673268</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
         <v>136</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C85">
+        <f t="shared" si="1"/>
+        <v>13.267326732673268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86">
         <v>136</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <f t="shared" si="1"/>
+        <v>13.267326732673268</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87">
         <v>136</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C87">
+        <f t="shared" si="1"/>
+        <v>13.267326732673268</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88">
         <v>138</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C88">
+        <f t="shared" si="1"/>
+        <v>15.267326732673268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89">
         <v>138</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C89">
+        <f t="shared" si="1"/>
+        <v>15.267326732673268</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90">
         <v>139</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C90">
+        <f t="shared" si="1"/>
+        <v>16.267326732673268</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91">
         <v>139</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C91">
+        <f t="shared" si="1"/>
+        <v>16.267326732673268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92">
         <v>141</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C92">
+        <f t="shared" si="1"/>
+        <v>18.267326732673268</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93">
         <v>142</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C93">
+        <f t="shared" si="1"/>
+        <v>19.267326732673268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
         <v>142</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C94">
+        <f t="shared" si="1"/>
+        <v>19.267326732673268</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95">
         <v>142</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C95">
+        <f t="shared" si="1"/>
+        <v>19.267326732673268</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96">
         <v>143</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C96">
+        <f t="shared" si="1"/>
+        <v>20.267326732673268</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97">
         <v>144</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C97">
+        <f t="shared" si="1"/>
+        <v>21.267326732673268</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98">
         <v>146</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C98">
+        <f t="shared" si="1"/>
+        <v>23.267326732673268</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
         <v>146</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C99">
+        <f t="shared" si="1"/>
+        <v>23.267326732673268</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100">
         <v>147</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C100">
+        <f t="shared" si="1"/>
+        <v>24.267326732673268</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101">
         <v>155</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C101">
+        <f t="shared" si="1"/>
+        <v>32.267326732673268</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102">
         <v>156</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="1"/>
+        <v>33.267326732673268</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C103" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103">
+        <f>SUM(D2:D102)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>2</v>
+      </c>
+      <c r="B104">
+        <f>AVERAGE(B2:B102)</f>
+        <v>122.73267326732673</v>
+      </c>
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104">
+        <f>D103/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105">
+        <v>123</v>
+      </c>
+      <c r="C105" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105">
+        <f>SQRT(D104)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
